--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,1598 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122393735</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105280</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>632869</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556877</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122394464</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92055</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>632866</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556763</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122394575</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92055</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnmossen, Björnmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>632866</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6556734</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122394081</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91219</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>632906</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6556844</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122397142</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90799</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>632877</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6556758</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122393382</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>632867</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557060</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122394626</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105280</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnmossen, Björnmossen, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>632874</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556728</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122394484</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105280</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>632865</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556760</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122393674</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105280</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupsjön, Djupsjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>632870</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556916</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122418985</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56584</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>632876</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556713</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122418563</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97131</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>632891</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556848</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Strax norr om bäcken.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122418572</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>632891</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556848</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122421266</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupsjön O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>632828</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6557060</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flertal ex.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122418533</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>632875</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6557018</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>92065</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393735</v>
+        <v>122393382</v>
       </c>
       <c r="B4" t="n">
-        <v>105280</v>
+        <v>56584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,34 +922,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632869</v>
+        <v>632867</v>
       </c>
       <c r="R4" t="n">
-        <v>6556877</v>
+        <v>6557060</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394464</v>
+        <v>122394626</v>
       </c>
       <c r="B5" t="n">
-        <v>92055</v>
+        <v>105290</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1039,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R5" t="n">
-        <v>6556763</v>
+        <v>6556728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394575</v>
+        <v>122393674</v>
       </c>
       <c r="B6" t="n">
-        <v>92055</v>
+        <v>105290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1151,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632866</v>
+        <v>632870</v>
       </c>
       <c r="R6" t="n">
-        <v>6556734</v>
+        <v>6556916</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394081</v>
+        <v>122394575</v>
       </c>
       <c r="B7" t="n">
-        <v>91219</v>
+        <v>92065</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1259,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632906</v>
+        <v>632866</v>
       </c>
       <c r="R7" t="n">
-        <v>6556844</v>
+        <v>6556734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122397142</v>
+        <v>122394464</v>
       </c>
       <c r="B8" t="n">
-        <v>90799</v>
+        <v>92065</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,48 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632877</v>
+        <v>632866</v>
       </c>
       <c r="R8" t="n">
-        <v>6556758</v>
+        <v>6556763</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393382</v>
+        <v>122397142</v>
       </c>
       <c r="B9" t="n">
-        <v>56584</v>
+        <v>90809</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,46 +1483,48 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632867</v>
+        <v>632877</v>
       </c>
       <c r="R9" t="n">
-        <v>6557060</v>
+        <v>6556758</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1578,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394626</v>
+        <v>122394081</v>
       </c>
       <c r="B10" t="n">
-        <v>105280</v>
+        <v>91229</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,38 +1602,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632874</v>
+        <v>632906</v>
       </c>
       <c r="R10" t="n">
-        <v>6556728</v>
+        <v>6556844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394484</v>
+        <v>122393735</v>
       </c>
       <c r="B11" t="n">
-        <v>105280</v>
+        <v>105290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632865</v>
+        <v>632869</v>
       </c>
       <c r="R11" t="n">
-        <v>6556760</v>
+        <v>6556877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393674</v>
+        <v>122394484</v>
       </c>
       <c r="B12" t="n">
-        <v>105280</v>
+        <v>105290</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632870</v>
+        <v>632865</v>
       </c>
       <c r="R12" t="n">
-        <v>6556916</v>
+        <v>6556760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418985</v>
+        <v>122418572</v>
       </c>
       <c r="B13" t="n">
-        <v>56584</v>
+        <v>100451</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,31 +1942,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1974,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R13" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2012,17 +2008,13 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2041,10 +2033,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418563</v>
+        <v>122421266</v>
       </c>
       <c r="B14" t="n">
-        <v>97131</v>
+        <v>100451</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,38 +2049,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R14" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2125,7 +2121,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,25 +2134,35 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418572</v>
+        <v>122418985</v>
       </c>
       <c r="B15" t="n">
-        <v>100451</v>
+        <v>56584</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,27 +2175,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2197,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R15" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2235,13 +2245,17 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2260,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122421266</v>
+        <v>122418563</v>
       </c>
       <c r="B16" t="n">
-        <v>100451</v>
+        <v>97131</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,42 +2290,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R16" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2348,7 +2358,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,25 +2371,15 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122393382</v>
+        <v>122394626</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>105290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,39 +922,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632867</v>
+        <v>632874</v>
       </c>
       <c r="R4" t="n">
-        <v>6557060</v>
+        <v>6556728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,7 +1018,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394626</v>
+        <v>122394484</v>
       </c>
       <c r="B5" t="n">
         <v>105290</v>
@@ -1059,14 +1054,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632874</v>
+        <v>632865</v>
       </c>
       <c r="R5" t="n">
-        <v>6556728</v>
+        <v>6556760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393674</v>
+        <v>122394464</v>
       </c>
       <c r="B6" t="n">
-        <v>105290</v>
+        <v>92065</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1146,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632870</v>
+        <v>632866</v>
       </c>
       <c r="R6" t="n">
-        <v>6556916</v>
+        <v>6556763</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394575</v>
+        <v>122393382</v>
       </c>
       <c r="B7" t="n">
-        <v>92065</v>
+        <v>56584</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,34 +1258,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632866</v>
+        <v>632867</v>
       </c>
       <c r="R7" t="n">
-        <v>6556734</v>
+        <v>6557060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122394464</v>
+        <v>122393735</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>105290</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632866</v>
+        <v>632869</v>
       </c>
       <c r="R8" t="n">
-        <v>6556763</v>
+        <v>6556877</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1471,10 +1471,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122397142</v>
+        <v>122394081</v>
       </c>
       <c r="B9" t="n">
-        <v>90809</v>
+        <v>91229</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,48 +1483,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632877</v>
+        <v>632906</v>
       </c>
       <c r="R9" t="n">
-        <v>6556758</v>
+        <v>6556844</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,22 +1571,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394081</v>
+        <v>122397142</v>
       </c>
       <c r="B10" t="n">
-        <v>91229</v>
+        <v>90809</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,41 +1595,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632906</v>
+        <v>632877</v>
       </c>
       <c r="R10" t="n">
-        <v>6556844</v>
+        <v>6556758</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1690,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393735</v>
+        <v>122394575</v>
       </c>
       <c r="B11" t="n">
-        <v>105290</v>
+        <v>92065</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1718,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R11" t="n">
-        <v>6556877</v>
+        <v>6556734</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394484</v>
+        <v>122393674</v>
       </c>
       <c r="B12" t="n">
         <v>105290</v>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632865</v>
+        <v>632870</v>
       </c>
       <c r="R12" t="n">
-        <v>6556760</v>
+        <v>6556916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,7 +1926,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418572</v>
+        <v>122418533</v>
       </c>
       <c r="B13" t="n">
         <v>100451</v>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R13" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122421266</v>
+        <v>122418563</v>
       </c>
       <c r="B14" t="n">
-        <v>100451</v>
+        <v>97131</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,42 +2054,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R14" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2121,7 +2122,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,25 +2135,15 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2274,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418563</v>
+        <v>122421266</v>
       </c>
       <c r="B16" t="n">
-        <v>97131</v>
+        <v>100451</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2290,38 +2281,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R16" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,22 +2366,32 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418533</v>
+        <v>122418572</v>
       </c>
       <c r="B17" t="n">
         <v>100451</v>
@@ -2430,10 +2435,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R17" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2468,11 +2473,6 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridda ex inom fuktdråg.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2495,6 +2495,135 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122442770</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105290</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djupsjön, O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>632838</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6557241</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Granskog.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394626</v>
+        <v>122394484</v>
       </c>
       <c r="B4" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,14 +942,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632874</v>
+        <v>632865</v>
       </c>
       <c r="R4" t="n">
-        <v>6556728</v>
+        <v>6556760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394484</v>
+        <v>122393382</v>
       </c>
       <c r="B5" t="n">
-        <v>105290</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1034,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632865</v>
+        <v>632867</v>
       </c>
       <c r="R5" t="n">
-        <v>6556760</v>
+        <v>6557060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1133,7 +1138,7 @@
         <v>122394464</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393382</v>
+        <v>122397142</v>
       </c>
       <c r="B7" t="n">
-        <v>56584</v>
+        <v>90821</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,46 +1259,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632867</v>
+        <v>632877</v>
       </c>
       <c r="R7" t="n">
-        <v>6557060</v>
+        <v>6556758</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,22 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393735</v>
+        <v>122393674</v>
       </c>
       <c r="B8" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1399,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632869</v>
+        <v>632870</v>
       </c>
       <c r="R8" t="n">
-        <v>6556877</v>
+        <v>6556916</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,7 +1481,7 @@
         <v>122394081</v>
       </c>
       <c r="B9" t="n">
-        <v>91229</v>
+        <v>91241</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1576,17 +1583,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397142</v>
+        <v>122393735</v>
       </c>
       <c r="B10" t="n">
-        <v>90809</v>
+        <v>105303</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,48 +1602,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632877</v>
+        <v>632869</v>
       </c>
       <c r="R10" t="n">
-        <v>6556758</v>
+        <v>6556877</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,12 +1690,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1705,7 +1705,7 @@
         <v>122394575</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393674</v>
+        <v>122394626</v>
       </c>
       <c r="B12" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1850,14 +1850,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632870</v>
+        <v>632874</v>
       </c>
       <c r="R12" t="n">
-        <v>6556916</v>
+        <v>6556728</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418533</v>
+        <v>122418563</v>
       </c>
       <c r="B13" t="n">
-        <v>100451</v>
+        <v>97143</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R13" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418563</v>
+        <v>122418985</v>
       </c>
       <c r="B14" t="n">
-        <v>97131</v>
+        <v>56589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,27 +2054,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224361</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2082,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R14" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2122,7 +2126,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2135,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2150,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418985</v>
+        <v>122418533</v>
       </c>
       <c r="B15" t="n">
-        <v>56584</v>
+        <v>100463</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,31 +2169,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632876</v>
+        <v>632875</v>
       </c>
       <c r="R15" t="n">
-        <v>6556713</v>
+        <v>6557018</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2238,7 +2237,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2247,6 +2246,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2265,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122421266</v>
+        <v>122418572</v>
       </c>
       <c r="B16" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,23 +2300,19 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R16" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2351,11 +2347,6 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flertal ex.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2366,35 +2357,25 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418572</v>
+        <v>122421266</v>
       </c>
       <c r="B17" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,19 +2407,23 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R17" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2473,6 +2458,11 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flertal ex.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2483,15 +2473,25 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105290</v>
+        <v>105303</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394484</v>
+        <v>122394081</v>
       </c>
       <c r="B4" t="n">
-        <v>105303</v>
+        <v>91246</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,25 +918,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632865</v>
+        <v>632906</v>
       </c>
       <c r="R4" t="n">
-        <v>6556760</v>
+        <v>6556844</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393382</v>
+        <v>122393674</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>105308</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,39 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632867</v>
+        <v>632870</v>
       </c>
       <c r="R5" t="n">
-        <v>6557060</v>
+        <v>6556916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,17 +1123,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394464</v>
+        <v>122397142</v>
       </c>
       <c r="B6" t="n">
-        <v>92077</v>
+        <v>90828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,41 +1142,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632866</v>
+        <v>632877</v>
       </c>
       <c r="R6" t="n">
-        <v>6556763</v>
+        <v>6556758</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397142</v>
+        <v>122394484</v>
       </c>
       <c r="B7" t="n">
-        <v>90821</v>
+        <v>105308</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,48 +1261,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632877</v>
+        <v>632865</v>
       </c>
       <c r="R7" t="n">
-        <v>6556758</v>
+        <v>6556760</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393674</v>
+        <v>122394575</v>
       </c>
       <c r="B8" t="n">
-        <v>105303</v>
+        <v>92082</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632870</v>
+        <v>632866</v>
       </c>
       <c r="R8" t="n">
-        <v>6556916</v>
+        <v>6556734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122394081</v>
+        <v>122393735</v>
       </c>
       <c r="B9" t="n">
-        <v>91241</v>
+        <v>105308</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,25 +1485,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632906</v>
+        <v>632869</v>
       </c>
       <c r="R9" t="n">
-        <v>6556844</v>
+        <v>6556877</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393735</v>
+        <v>122394464</v>
       </c>
       <c r="B10" t="n">
-        <v>105303</v>
+        <v>92082</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R10" t="n">
-        <v>6556877</v>
+        <v>6556763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394575</v>
+        <v>122393382</v>
       </c>
       <c r="B11" t="n">
-        <v>92077</v>
+        <v>56589</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1713,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632866</v>
+        <v>632867</v>
       </c>
       <c r="R11" t="n">
-        <v>6556734</v>
+        <v>6557060</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,7 +1807,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1817,7 +1817,7 @@
         <v>122394626</v>
       </c>
       <c r="B12" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418563</v>
+        <v>122421266</v>
       </c>
       <c r="B13" t="n">
-        <v>97143</v>
+        <v>100468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,38 +1942,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R13" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,25 +2027,35 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418985</v>
+        <v>122418533</v>
       </c>
       <c r="B14" t="n">
-        <v>56589</v>
+        <v>100468</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,31 +2068,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,10 +2096,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632876</v>
+        <v>632875</v>
       </c>
       <c r="R14" t="n">
-        <v>6556713</v>
+        <v>6557018</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2136,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2135,6 +2145,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2153,10 +2164,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418533</v>
+        <v>122418572</v>
       </c>
       <c r="B15" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R15" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,11 +2244,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418572</v>
+        <v>122418563</v>
       </c>
       <c r="B16" t="n">
-        <v>100463</v>
+        <v>97148</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,21 +2287,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,6 +2353,11 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Strax norr om bäcken.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2372,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122421266</v>
+        <v>122418985</v>
       </c>
       <c r="B17" t="n">
-        <v>100463</v>
+        <v>56589</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,42 +2399,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632828</v>
+        <v>632876</v>
       </c>
       <c r="R17" t="n">
-        <v>6557060</v>
+        <v>6556713</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2460,7 +2471,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,29 +2480,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105303</v>
+        <v>105308</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -1697,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393382</v>
+        <v>122394626</v>
       </c>
       <c r="B11" t="n">
-        <v>56589</v>
+        <v>105308</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,39 +1713,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632867</v>
+        <v>632874</v>
       </c>
       <c r="R11" t="n">
-        <v>6557060</v>
+        <v>6556728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1772,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1782,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,17 +1802,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394626</v>
+        <v>122393382</v>
       </c>
       <c r="B12" t="n">
-        <v>105308</v>
+        <v>56589</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1825,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632874</v>
+        <v>632867</v>
       </c>
       <c r="R12" t="n">
-        <v>6556728</v>
+        <v>6557060</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,11 +818,6 @@
       </c>
       <c r="E3" t="n">
         <v>4364</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -906,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394081</v>
+        <v>122394575</v>
       </c>
       <c r="B4" t="n">
-        <v>91246</v>
+        <v>92087</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,38 +913,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632906</v>
+        <v>632866</v>
       </c>
       <c r="R4" t="n">
-        <v>6556844</v>
+        <v>6556734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,17 +1001,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393674</v>
+        <v>122393382</v>
       </c>
       <c r="B5" t="n">
-        <v>105308</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1024,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632870</v>
+        <v>632867</v>
       </c>
       <c r="R5" t="n">
-        <v>6556916</v>
+        <v>6557060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,17 +1113,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397142</v>
+        <v>122394484</v>
       </c>
       <c r="B6" t="n">
-        <v>90828</v>
+        <v>105317</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,48 +1132,36 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632877</v>
+        <v>632865</v>
       </c>
       <c r="R6" t="n">
-        <v>6556758</v>
+        <v>6556760</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1190,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1200,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1215,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394484</v>
+        <v>122393674</v>
       </c>
       <c r="B7" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,11 +1245,6 @@
       <c r="E7" t="n">
         <v>221144</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Pyrola chlorantha</t>
@@ -1289,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632865</v>
+        <v>632870</v>
       </c>
       <c r="R7" t="n">
-        <v>6556760</v>
+        <v>6556916</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1307,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,17 +1327,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122394575</v>
+        <v>122394464</v>
       </c>
       <c r="B8" t="n">
-        <v>92082</v>
+        <v>92087</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,11 +1352,6 @@
       <c r="E8" t="n">
         <v>4364</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Hydnellum ferrugineum</t>
@@ -1397,14 +1365,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>632866</v>
       </c>
       <c r="R8" t="n">
-        <v>6556734</v>
+        <v>6556763</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1404,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1414,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393735</v>
+        <v>122394081</v>
       </c>
       <c r="B9" t="n">
-        <v>105308</v>
+        <v>91251</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1453,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
+        <v>1209</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632869</v>
+        <v>632906</v>
       </c>
       <c r="R9" t="n">
-        <v>6556877</v>
+        <v>6556844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,17 +1541,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394464</v>
+        <v>122394626</v>
       </c>
       <c r="B10" t="n">
-        <v>92082</v>
+        <v>105317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,34 +1564,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>221144</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R10" t="n">
-        <v>6556763</v>
+        <v>6556728</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1618,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1628,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394626</v>
+        <v>122393735</v>
       </c>
       <c r="B11" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,11 +1673,6 @@
       <c r="E11" t="n">
         <v>221144</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Pyrola chlorantha</t>
@@ -1733,14 +1686,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632874</v>
+        <v>632869</v>
       </c>
       <c r="R11" t="n">
-        <v>6556728</v>
+        <v>6556877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1772,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1782,7 +1735,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,10 +1762,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393382</v>
+        <v>122397142</v>
       </c>
       <c r="B12" t="n">
-        <v>56589</v>
+        <v>90833</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,46 +1774,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632867</v>
+        <v>632877</v>
       </c>
       <c r="R12" t="n">
-        <v>6557060</v>
+        <v>6556758</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,12 +1864,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1929,7 +1879,7 @@
         <v>122421266</v>
       </c>
       <c r="B13" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,11 +1893,6 @@
       </c>
       <c r="E13" t="n">
         <v>222498</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2052,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418533</v>
+        <v>122418985</v>
       </c>
       <c r="B14" t="n">
-        <v>100468</v>
+        <v>56589</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2068,27 +2013,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>100138</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2096,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632875</v>
+        <v>632876</v>
       </c>
       <c r="R14" t="n">
-        <v>6557018</v>
+        <v>6556713</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2136,7 +2080,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,7 +2089,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2167,7 +2110,7 @@
         <v>122418572</v>
       </c>
       <c r="B15" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,11 +2124,6 @@
       </c>
       <c r="E15" t="n">
         <v>222498</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2271,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418563</v>
+        <v>122418533</v>
       </c>
       <c r="B16" t="n">
-        <v>97148</v>
+        <v>100477</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,21 +2225,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224361</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Äkta lopplummer</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2315,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R16" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2355,7 +2288,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,10 +2316,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418985</v>
+        <v>122418563</v>
       </c>
       <c r="B17" t="n">
-        <v>56589</v>
+        <v>97157</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,31 +2332,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>224361</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2431,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R17" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,7 +2395,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,6 +2404,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2501,7 +2426,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105308</v>
+        <v>105317</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,11 +2440,6 @@
       </c>
       <c r="E18" t="n">
         <v>221144</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -1441,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122394081</v>
+        <v>122394626</v>
       </c>
       <c r="B9" t="n">
-        <v>91251</v>
+        <v>105317</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1453,33 +1453,33 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632906</v>
+        <v>632874</v>
       </c>
       <c r="R9" t="n">
-        <v>6556844</v>
+        <v>6556728</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394626</v>
+        <v>122393735</v>
       </c>
       <c r="B10" t="n">
         <v>105317</v>
@@ -1579,14 +1579,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632874</v>
+        <v>632869</v>
       </c>
       <c r="R10" t="n">
-        <v>6556728</v>
+        <v>6556877</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1655,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393735</v>
+        <v>122394081</v>
       </c>
       <c r="B11" t="n">
-        <v>105317</v>
+        <v>91251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,20 +1667,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632869</v>
+        <v>632906</v>
       </c>
       <c r="R11" t="n">
-        <v>6556877</v>
+        <v>6556844</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,6 +818,11 @@
       </c>
       <c r="E3" t="n">
         <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -901,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394575</v>
+        <v>122394626</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>105330</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,16 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R4" t="n">
-        <v>6556734</v>
+        <v>6556728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393382</v>
+        <v>122393735</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>105330</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,34 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632867</v>
+        <v>632869</v>
       </c>
       <c r="R5" t="n">
-        <v>6557060</v>
+        <v>6556877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1093,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1113,17 +1123,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394484</v>
+        <v>122397142</v>
       </c>
       <c r="B6" t="n">
-        <v>105317</v>
+        <v>90846</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,36 +1142,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632865</v>
+        <v>632877</v>
       </c>
       <c r="R6" t="n">
-        <v>6556760</v>
+        <v>6556758</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1190,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1200,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393674</v>
+        <v>122393382</v>
       </c>
       <c r="B7" t="n">
-        <v>105317</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1243,29 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100138</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632870</v>
+        <v>632867</v>
       </c>
       <c r="R7" t="n">
-        <v>6556916</v>
+        <v>6557060</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1307,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,17 +1359,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122394464</v>
+        <v>122394575</v>
       </c>
       <c r="B8" t="n">
-        <v>92087</v>
+        <v>92100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,6 +1384,11 @@
       <c r="E8" t="n">
         <v>4364</v>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Hydnellum ferrugineum</t>
@@ -1365,14 +1402,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>632866</v>
       </c>
       <c r="R8" t="n">
-        <v>6556763</v>
+        <v>6556734</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122394626</v>
+        <v>122393674</v>
       </c>
       <c r="B9" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,6 +1496,11 @@
       <c r="E9" t="n">
         <v>221144</v>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Pyrola chlorantha</t>
@@ -1472,14 +1514,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632874</v>
+        <v>632870</v>
       </c>
       <c r="R9" t="n">
-        <v>6556728</v>
+        <v>6556916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1521,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393735</v>
+        <v>122394464</v>
       </c>
       <c r="B10" t="n">
-        <v>105317</v>
+        <v>92100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,16 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1583,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R10" t="n">
-        <v>6556877</v>
+        <v>6556763</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1628,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,7 +1705,7 @@
         <v>122394081</v>
       </c>
       <c r="B11" t="n">
-        <v>91251</v>
+        <v>91264</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,6 +1719,11 @@
       </c>
       <c r="E11" t="n">
         <v>1209</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1762,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397142</v>
+        <v>122394484</v>
       </c>
       <c r="B12" t="n">
-        <v>90833</v>
+        <v>105330</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,43 +1826,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632877</v>
+        <v>632865</v>
       </c>
       <c r="R12" t="n">
-        <v>6556758</v>
+        <v>6556760</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1839,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,22 +1914,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122421266</v>
+        <v>122418533</v>
       </c>
       <c r="B13" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1894,6 +1944,11 @@
       <c r="E13" t="n">
         <v>222498</v>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Hepatica nobilis</t>
@@ -1906,23 +1961,19 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632828</v>
+        <v>632875</v>
       </c>
       <c r="R13" t="n">
-        <v>6557060</v>
+        <v>6557018</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1959,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,35 +2023,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418985</v>
+        <v>122421266</v>
       </c>
       <c r="B14" t="n">
-        <v>56589</v>
+        <v>100490</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,37 +2054,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632876</v>
+        <v>632828</v>
       </c>
       <c r="R14" t="n">
-        <v>6556713</v>
+        <v>6557060</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2080,7 +2126,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,28 +2135,39 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418572</v>
+        <v>122418563</v>
       </c>
       <c r="B15" t="n">
-        <v>100477</v>
+        <v>97170</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2123,16 +2180,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>224361</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2184,6 +2246,11 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Strax norr om bäcken.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2209,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418533</v>
+        <v>122418572</v>
       </c>
       <c r="B16" t="n">
-        <v>100477</v>
+        <v>100490</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2226,6 +2293,11 @@
       </c>
       <c r="E16" t="n">
         <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2248,10 +2320,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R16" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2284,11 +2356,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418563</v>
+        <v>122418985</v>
       </c>
       <c r="B17" t="n">
-        <v>97157</v>
+        <v>56593</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2332,22 +2399,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224361</v>
+        <v>100138</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2355,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R17" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,7 +2471,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2404,7 +2480,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2426,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2440,6 +2515,11 @@
       </c>
       <c r="E18" t="n">
         <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>122394626</v>
       </c>
       <c r="B4" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>122393735</v>
       </c>
       <c r="B5" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397142</v>
+        <v>122393674</v>
       </c>
       <c r="B6" t="n">
-        <v>90846</v>
+        <v>105343</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,48 +1142,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632877</v>
+        <v>632870</v>
       </c>
       <c r="R6" t="n">
-        <v>6556758</v>
+        <v>6556916</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393382</v>
+        <v>122394484</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>105343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,39 +1258,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632867</v>
+        <v>632865</v>
       </c>
       <c r="R7" t="n">
-        <v>6557060</v>
+        <v>6556760</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1354,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122394575</v>
+        <v>122397142</v>
       </c>
       <c r="B8" t="n">
-        <v>92100</v>
+        <v>90859</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,41 +1366,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632866</v>
+        <v>632877</v>
       </c>
       <c r="R8" t="n">
-        <v>6556734</v>
+        <v>6556758</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393674</v>
+        <v>122393382</v>
       </c>
       <c r="B9" t="n">
-        <v>105330</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632870</v>
+        <v>632867</v>
       </c>
       <c r="R9" t="n">
-        <v>6556916</v>
+        <v>6557060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394464</v>
+        <v>122394575</v>
       </c>
       <c r="B10" t="n">
-        <v>92100</v>
+        <v>92113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,14 +1626,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>632866</v>
       </c>
       <c r="R10" t="n">
-        <v>6556763</v>
+        <v>6556734</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,7 +1705,7 @@
         <v>122394081</v>
       </c>
       <c r="B11" t="n">
-        <v>91264</v>
+        <v>91277</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394484</v>
+        <v>122394464</v>
       </c>
       <c r="B12" t="n">
-        <v>105330</v>
+        <v>92113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1830,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632865</v>
+        <v>632866</v>
       </c>
       <c r="R12" t="n">
-        <v>6556760</v>
+        <v>6556763</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1919,17 +1919,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418533</v>
+        <v>122418572</v>
       </c>
       <c r="B13" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R13" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,11 +2006,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2036,7 @@
         <v>122421266</v>
       </c>
       <c r="B14" t="n">
-        <v>100490</v>
+        <v>100503</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418563</v>
+        <v>122418533</v>
       </c>
       <c r="B15" t="n">
-        <v>97170</v>
+        <v>100503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,21 +2175,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R15" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2248,7 +2243,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418572</v>
+        <v>122418985</v>
       </c>
       <c r="B16" t="n">
-        <v>100490</v>
+        <v>56593</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,27 +2287,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2320,10 +2319,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R16" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2358,13 +2357,17 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2383,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418985</v>
+        <v>122418563</v>
       </c>
       <c r="B17" t="n">
-        <v>56593</v>
+        <v>97183</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,31 +2402,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>224361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2431,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R17" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,7 +2470,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,6 +2479,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393382</v>
+        <v>122394575</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>92113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632867</v>
+        <v>632866</v>
       </c>
       <c r="R9" t="n">
-        <v>6557060</v>
+        <v>6556734</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,17 +1578,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394575</v>
+        <v>122393382</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>56593</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1601,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632866</v>
+        <v>632867</v>
       </c>
       <c r="R10" t="n">
-        <v>6556734</v>
+        <v>6557060</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394081</v>
+        <v>122394464</v>
       </c>
       <c r="B11" t="n">
-        <v>91277</v>
+        <v>92113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,25 +1714,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632906</v>
+        <v>632866</v>
       </c>
       <c r="R11" t="n">
-        <v>6556844</v>
+        <v>6556763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394464</v>
+        <v>122394081</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>91277</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,25 +1826,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632866</v>
+        <v>632906</v>
       </c>
       <c r="R12" t="n">
-        <v>6556763</v>
+        <v>6556844</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394626</v>
+        <v>122394484</v>
       </c>
       <c r="B4" t="n">
         <v>105343</v>
@@ -942,14 +942,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632874</v>
+        <v>632865</v>
       </c>
       <c r="R4" t="n">
-        <v>6556728</v>
+        <v>6556760</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393735</v>
+        <v>122394575</v>
       </c>
       <c r="B5" t="n">
-        <v>105343</v>
+        <v>92113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R5" t="n">
-        <v>6556877</v>
+        <v>6556734</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,7 +1130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393674</v>
+        <v>122394626</v>
       </c>
       <c r="B6" t="n">
         <v>105343</v>
@@ -1166,14 +1166,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632870</v>
+        <v>632874</v>
       </c>
       <c r="R6" t="n">
-        <v>6556916</v>
+        <v>6556728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394484</v>
+        <v>122393735</v>
       </c>
       <c r="B7" t="n">
         <v>105343</v>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632865</v>
+        <v>632869</v>
       </c>
       <c r="R7" t="n">
-        <v>6556760</v>
+        <v>6556877</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,17 +1347,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122397142</v>
+        <v>122393382</v>
       </c>
       <c r="B8" t="n">
-        <v>90859</v>
+        <v>56593</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,48 +1366,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632877</v>
+        <v>632867</v>
       </c>
       <c r="R8" t="n">
-        <v>6556758</v>
+        <v>6557060</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122394575</v>
+        <v>122393674</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>105343</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1487,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632866</v>
+        <v>632870</v>
       </c>
       <c r="R9" t="n">
-        <v>6556734</v>
+        <v>6556916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122393382</v>
+        <v>122394081</v>
       </c>
       <c r="B10" t="n">
-        <v>56593</v>
+        <v>91277</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,43 +1595,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632867</v>
+        <v>632906</v>
       </c>
       <c r="R10" t="n">
-        <v>6557060</v>
+        <v>6556844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1814,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394081</v>
+        <v>122397142</v>
       </c>
       <c r="B12" t="n">
-        <v>91277</v>
+        <v>90859</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,41 +1819,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632906</v>
+        <v>632877</v>
       </c>
       <c r="R12" t="n">
-        <v>6556844</v>
+        <v>6556758</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,19 +1914,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418572</v>
+        <v>122418533</v>
       </c>
       <c r="B13" t="n">
         <v>100503</v>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R13" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2006,6 +2006,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122421266</v>
+        <v>122418563</v>
       </c>
       <c r="B14" t="n">
-        <v>100503</v>
+        <v>97183</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2049,42 +2054,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R14" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2121,7 +2122,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2134,35 +2135,25 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418533</v>
+        <v>122418985</v>
       </c>
       <c r="B15" t="n">
-        <v>100503</v>
+        <v>56593</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,27 +2166,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2203,10 +2198,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632875</v>
+        <v>632876</v>
       </c>
       <c r="R15" t="n">
-        <v>6557018</v>
+        <v>6556713</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2243,7 +2238,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2252,7 +2247,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2271,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418985</v>
+        <v>122421266</v>
       </c>
       <c r="B16" t="n">
-        <v>56593</v>
+        <v>100503</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2287,42 +2281,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632876</v>
+        <v>632828</v>
       </c>
       <c r="R16" t="n">
-        <v>6556713</v>
+        <v>6557060</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2359,7 +2353,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,28 +2362,39 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418563</v>
+        <v>122418572</v>
       </c>
       <c r="B17" t="n">
-        <v>97183</v>
+        <v>100503</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2468,11 +2473,6 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Strax norr om bäcken.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394484</v>
+        <v>122394464</v>
       </c>
       <c r="B4" t="n">
-        <v>105343</v>
+        <v>92114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632865</v>
+        <v>632866</v>
       </c>
       <c r="R4" t="n">
-        <v>6556760</v>
+        <v>6556763</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394575</v>
+        <v>122393674</v>
       </c>
       <c r="B5" t="n">
-        <v>92113</v>
+        <v>105346</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632866</v>
+        <v>632870</v>
       </c>
       <c r="R5" t="n">
-        <v>6556734</v>
+        <v>6556916</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122394626</v>
+        <v>122397142</v>
       </c>
       <c r="B6" t="n">
-        <v>105343</v>
+        <v>90853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,41 +1142,48 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632874</v>
+        <v>632877</v>
       </c>
       <c r="R6" t="n">
-        <v>6556728</v>
+        <v>6556758</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122393735</v>
+        <v>122394575</v>
       </c>
       <c r="B7" t="n">
-        <v>105343</v>
+        <v>92114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,34 +1265,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R7" t="n">
-        <v>6556877</v>
+        <v>6556734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1471,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393674</v>
+        <v>122394081</v>
       </c>
       <c r="B9" t="n">
-        <v>105343</v>
+        <v>91278</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,25 +1490,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1511,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632870</v>
+        <v>632906</v>
       </c>
       <c r="R9" t="n">
-        <v>6556916</v>
+        <v>6556844</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,17 +1583,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394081</v>
+        <v>122394484</v>
       </c>
       <c r="B10" t="n">
-        <v>91277</v>
+        <v>105346</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632906</v>
+        <v>632865</v>
       </c>
       <c r="R10" t="n">
-        <v>6556844</v>
+        <v>6556760</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394464</v>
+        <v>122394626</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>105346</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,34 +1718,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R11" t="n">
-        <v>6556763</v>
+        <v>6556728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122397142</v>
+        <v>122393735</v>
       </c>
       <c r="B12" t="n">
-        <v>90859</v>
+        <v>105346</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,48 +1826,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632877</v>
+        <v>632869</v>
       </c>
       <c r="R12" t="n">
-        <v>6556758</v>
+        <v>6556877</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,22 +1914,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418533</v>
+        <v>122418563</v>
       </c>
       <c r="B13" t="n">
-        <v>100503</v>
+        <v>97186</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1970,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632875</v>
+        <v>632891</v>
       </c>
       <c r="R13" t="n">
-        <v>6557018</v>
+        <v>6556848</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418563</v>
+        <v>122418985</v>
       </c>
       <c r="B14" t="n">
-        <v>97183</v>
+        <v>56593</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,27 +2054,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>224361</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2082,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R14" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2122,7 +2126,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,7 +2135,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2150,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418985</v>
+        <v>122418572</v>
       </c>
       <c r="B15" t="n">
-        <v>56593</v>
+        <v>100506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,31 +2169,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2198,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R15" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2236,17 +2235,13 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2268,7 +2263,7 @@
         <v>122421266</v>
       </c>
       <c r="B16" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2391,10 +2386,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418572</v>
+        <v>122418533</v>
       </c>
       <c r="B17" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R17" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,6 +2466,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394464</v>
+        <v>122394626</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>105346</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,34 +922,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R4" t="n">
-        <v>6556763</v>
+        <v>6556728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122393674</v>
+        <v>122394464</v>
       </c>
       <c r="B5" t="n">
-        <v>105346</v>
+        <v>92114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632870</v>
+        <v>632866</v>
       </c>
       <c r="R5" t="n">
-        <v>6556916</v>
+        <v>6556763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122397142</v>
+        <v>122393674</v>
       </c>
       <c r="B6" t="n">
-        <v>90853</v>
+        <v>105346</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,48 +1142,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632877</v>
+        <v>632870</v>
       </c>
       <c r="R6" t="n">
-        <v>6556758</v>
+        <v>6556916</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394575</v>
+        <v>122397142</v>
       </c>
       <c r="B7" t="n">
-        <v>92114</v>
+        <v>90853</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,41 +1254,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632866</v>
+        <v>632877</v>
       </c>
       <c r="R7" t="n">
-        <v>6556734</v>
+        <v>6556758</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393382</v>
+        <v>122394081</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>91278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,43 +1373,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632867</v>
+        <v>632906</v>
       </c>
       <c r="R8" t="n">
-        <v>6557060</v>
+        <v>6556844</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122394081</v>
+        <v>122393382</v>
       </c>
       <c r="B9" t="n">
-        <v>91278</v>
+        <v>56593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,38 +1485,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632906</v>
+        <v>632867</v>
       </c>
       <c r="R9" t="n">
-        <v>6556844</v>
+        <v>6557060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394626</v>
+        <v>122393735</v>
       </c>
       <c r="B11" t="n">
         <v>105346</v>
@@ -1738,14 +1738,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632874</v>
+        <v>632869</v>
       </c>
       <c r="R11" t="n">
-        <v>6556728</v>
+        <v>6556877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393735</v>
+        <v>122394575</v>
       </c>
       <c r="B12" t="n">
-        <v>105346</v>
+        <v>92114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632869</v>
+        <v>632866</v>
       </c>
       <c r="R12" t="n">
-        <v>6556877</v>
+        <v>6556734</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2038,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418985</v>
+        <v>122418572</v>
       </c>
       <c r="B14" t="n">
-        <v>56593</v>
+        <v>100506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,31 +2054,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2086,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R14" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2124,17 +2120,13 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2153,7 +2145,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418572</v>
+        <v>122418533</v>
       </c>
       <c r="B15" t="n">
         <v>100506</v>
@@ -2197,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R15" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,6 +2225,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2386,10 +2383,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418533</v>
+        <v>122418985</v>
       </c>
       <c r="B17" t="n">
-        <v>100506</v>
+        <v>56593</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,27 +2399,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2430,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632875</v>
+        <v>632876</v>
       </c>
       <c r="R17" t="n">
-        <v>6557018</v>
+        <v>6556713</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2470,7 +2471,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2479,7 +2480,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>122263529</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394626</v>
+        <v>122394575</v>
       </c>
       <c r="B4" t="n">
-        <v>105346</v>
+        <v>92115</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632874</v>
+        <v>632866</v>
       </c>
       <c r="R4" t="n">
-        <v>6556728</v>
+        <v>6556734</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
         <v>122394464</v>
       </c>
       <c r="B5" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1130,10 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393674</v>
+        <v>122393735</v>
       </c>
       <c r="B6" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632870</v>
+        <v>632869</v>
       </c>
       <c r="R6" t="n">
-        <v>6556916</v>
+        <v>6556877</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122397142</v>
+        <v>122394081</v>
       </c>
       <c r="B7" t="n">
-        <v>90853</v>
+        <v>91279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,48 +1254,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632877</v>
+        <v>632906</v>
       </c>
       <c r="R7" t="n">
-        <v>6556758</v>
+        <v>6556844</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1342,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122394081</v>
+        <v>122397142</v>
       </c>
       <c r="B8" t="n">
-        <v>91278</v>
+        <v>90854</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,41 +1366,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632906</v>
+        <v>632877</v>
       </c>
       <c r="R8" t="n">
-        <v>6556844</v>
+        <v>6556758</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,12 +1461,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1476,7 +1476,7 @@
         <v>122393382</v>
       </c>
       <c r="B9" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>122394484</v>
       </c>
       <c r="B10" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122393735</v>
+        <v>122394626</v>
       </c>
       <c r="B11" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,14 +1738,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632869</v>
+        <v>632874</v>
       </c>
       <c r="R11" t="n">
-        <v>6556877</v>
+        <v>6556728</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394575</v>
+        <v>122393674</v>
       </c>
       <c r="B12" t="n">
-        <v>92114</v>
+        <v>105347</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1830,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632866</v>
+        <v>632870</v>
       </c>
       <c r="R12" t="n">
-        <v>6556734</v>
+        <v>6556916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418563</v>
+        <v>122421266</v>
       </c>
       <c r="B13" t="n">
-        <v>97186</v>
+        <v>100507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,38 +1942,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R13" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2010,7 +2014,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2023,15 +2027,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2041,7 +2055,7 @@
         <v>122418572</v>
       </c>
       <c r="B14" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2145,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418533</v>
+        <v>122418985</v>
       </c>
       <c r="B15" t="n">
-        <v>100506</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,27 +2175,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2207,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632875</v>
+        <v>632876</v>
       </c>
       <c r="R15" t="n">
-        <v>6557018</v>
+        <v>6556713</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,7 +2247,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2256,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2274,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122421266</v>
+        <v>122418533</v>
       </c>
       <c r="B16" t="n">
-        <v>100506</v>
+        <v>100507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,23 +2309,19 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632828</v>
+        <v>632875</v>
       </c>
       <c r="R16" t="n">
-        <v>6557060</v>
+        <v>6557018</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2345,7 +2358,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2358,35 +2371,25 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418985</v>
+        <v>122418563</v>
       </c>
       <c r="B17" t="n">
-        <v>56593</v>
+        <v>97187</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2399,31 +2402,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>224361</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2431,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R17" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2471,7 +2470,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2480,6 +2479,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394575</v>
+        <v>122394626</v>
       </c>
       <c r="B4" t="n">
-        <v>92115</v>
+        <v>105350</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -922,21 +922,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632866</v>
+        <v>632874</v>
       </c>
       <c r="R4" t="n">
-        <v>6556734</v>
+        <v>6556728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394464</v>
+        <v>122394484</v>
       </c>
       <c r="B5" t="n">
-        <v>92115</v>
+        <v>105350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632866</v>
+        <v>632865</v>
       </c>
       <c r="R5" t="n">
-        <v>6556763</v>
+        <v>6556760</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393735</v>
+        <v>122393382</v>
       </c>
       <c r="B6" t="n">
-        <v>105347</v>
+        <v>56594</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,34 +1146,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632869</v>
+        <v>632867</v>
       </c>
       <c r="R6" t="n">
-        <v>6556877</v>
+        <v>6557060</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,17 +1240,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394081</v>
+        <v>122394575</v>
       </c>
       <c r="B7" t="n">
-        <v>91279</v>
+        <v>92118</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,38 +1259,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632906</v>
+        <v>632866</v>
       </c>
       <c r="R7" t="n">
-        <v>6556844</v>
+        <v>6556734</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,7 +1352,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1357,7 +1362,7 @@
         <v>122397142</v>
       </c>
       <c r="B8" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393382</v>
+        <v>122393674</v>
       </c>
       <c r="B9" t="n">
-        <v>56594</v>
+        <v>105350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632867</v>
+        <v>632870</v>
       </c>
       <c r="R9" t="n">
-        <v>6557060</v>
+        <v>6556916</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,17 +1583,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394484</v>
+        <v>122394081</v>
       </c>
       <c r="B10" t="n">
-        <v>105347</v>
+        <v>91282</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632865</v>
+        <v>632906</v>
       </c>
       <c r="R10" t="n">
-        <v>6556760</v>
+        <v>6556844</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394626</v>
+        <v>122394464</v>
       </c>
       <c r="B11" t="n">
-        <v>105347</v>
+        <v>92118</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1718,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632874</v>
+        <v>632866</v>
       </c>
       <c r="R11" t="n">
-        <v>6556728</v>
+        <v>6556763</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393674</v>
+        <v>122393735</v>
       </c>
       <c r="B12" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632870</v>
+        <v>632869</v>
       </c>
       <c r="R12" t="n">
-        <v>6556916</v>
+        <v>6556877</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122421266</v>
+        <v>122418563</v>
       </c>
       <c r="B13" t="n">
-        <v>100507</v>
+        <v>97190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,42 +1942,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R13" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2014,7 +2010,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,35 +2023,25 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418572</v>
+        <v>122418533</v>
       </c>
       <c r="B14" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,10 +2082,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632891</v>
+        <v>632875</v>
       </c>
       <c r="R14" t="n">
-        <v>6556848</v>
+        <v>6557018</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2132,6 +2118,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418533</v>
+        <v>122421266</v>
       </c>
       <c r="B16" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2309,19 +2300,23 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632875</v>
+        <v>632828</v>
       </c>
       <c r="R16" t="n">
-        <v>6557018</v>
+        <v>6557060</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2358,7 +2353,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Spridda ex inom fuktdråg.</t>
+          <t>Flertal ex.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,25 +2366,35 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418563</v>
+        <v>122418572</v>
       </c>
       <c r="B17" t="n">
-        <v>97187</v>
+        <v>100510</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2402,21 +2407,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2468,11 +2473,6 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Strax norr om bäcken.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394626</v>
+        <v>122393735</v>
       </c>
       <c r="B4" t="n">
         <v>105350</v>
@@ -942,14 +942,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632874</v>
+        <v>632869</v>
       </c>
       <c r="R4" t="n">
-        <v>6556728</v>
+        <v>6556877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394484</v>
+        <v>122393382</v>
       </c>
       <c r="B5" t="n">
-        <v>105350</v>
+        <v>56594</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,34 +1034,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632865</v>
+        <v>632867</v>
       </c>
       <c r="R5" t="n">
-        <v>6556760</v>
+        <v>6557060</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393382</v>
+        <v>122394626</v>
       </c>
       <c r="B6" t="n">
-        <v>56594</v>
+        <v>105350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,39 +1151,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632867</v>
+        <v>632874</v>
       </c>
       <c r="R6" t="n">
-        <v>6557060</v>
+        <v>6556728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122397142</v>
+        <v>122394081</v>
       </c>
       <c r="B8" t="n">
-        <v>90857</v>
+        <v>91282</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,48 +1371,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632877</v>
+        <v>632906</v>
       </c>
       <c r="R8" t="n">
-        <v>6556758</v>
+        <v>6556844</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1441,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1444,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1459,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393674</v>
+        <v>122394464</v>
       </c>
       <c r="B9" t="n">
-        <v>105350</v>
+        <v>92118</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,21 +1487,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1518,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632870</v>
+        <v>632866</v>
       </c>
       <c r="R9" t="n">
-        <v>6556916</v>
+        <v>6556763</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122394081</v>
+        <v>122397142</v>
       </c>
       <c r="B10" t="n">
-        <v>91282</v>
+        <v>90857</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,41 +1595,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632906</v>
+        <v>632877</v>
       </c>
       <c r="R10" t="n">
-        <v>6556844</v>
+        <v>6556758</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1690,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394464</v>
+        <v>122393674</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>105350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632866</v>
+        <v>632870</v>
       </c>
       <c r="R11" t="n">
-        <v>6556763</v>
+        <v>6556916</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122393735</v>
+        <v>122394484</v>
       </c>
       <c r="B12" t="n">
         <v>105350</v>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632869</v>
+        <v>632865</v>
       </c>
       <c r="R12" t="n">
-        <v>6556877</v>
+        <v>6556760</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418563</v>
+        <v>122418572</v>
       </c>
       <c r="B13" t="n">
-        <v>97190</v>
+        <v>100510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>224361</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2008,11 +2008,6 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Strax norr om bäcken.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2265,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122421266</v>
+        <v>122418563</v>
       </c>
       <c r="B16" t="n">
-        <v>100510</v>
+        <v>97190</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,42 +2276,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>224361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632828</v>
+        <v>632891</v>
       </c>
       <c r="R16" t="n">
-        <v>6557060</v>
+        <v>6556848</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2353,7 +2344,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flertal ex.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,32 +2357,22 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418572</v>
+        <v>122421266</v>
       </c>
       <c r="B17" t="n">
         <v>100510</v>
@@ -2426,19 +2407,23 @@
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632891</v>
+        <v>632828</v>
       </c>
       <c r="R17" t="n">
-        <v>6556848</v>
+        <v>6557060</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2473,6 +2458,11 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Flertal ex.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2483,15 +2473,25 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -2145,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418985</v>
+        <v>122418563</v>
       </c>
       <c r="B15" t="n">
-        <v>56594</v>
+        <v>97190</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,31 +2161,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>224361</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2193,10 +2189,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R15" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2233,7 +2229,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2242,6 +2238,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2260,10 +2257,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418563</v>
+        <v>122418985</v>
       </c>
       <c r="B16" t="n">
-        <v>97190</v>
+        <v>56594</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2276,27 +2273,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224361</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2304,10 +2305,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R16" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2344,7 +2345,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2353,7 +2354,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -2145,10 +2145,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122418563</v>
+        <v>122418985</v>
       </c>
       <c r="B15" t="n">
-        <v>97190</v>
+        <v>56594</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,27 +2161,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>224361</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Björk</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2189,10 +2193,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632891</v>
+        <v>632876</v>
       </c>
       <c r="R15" t="n">
-        <v>6556848</v>
+        <v>6556713</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2229,7 +2233,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2242,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2257,10 +2260,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418985</v>
+        <v>122418563</v>
       </c>
       <c r="B16" t="n">
-        <v>56594</v>
+        <v>97190</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2273,31 +2276,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>224361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Äkta lopplummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Huperzia europaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Björk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2305,10 +2304,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632876</v>
+        <v>632891</v>
       </c>
       <c r="R16" t="n">
-        <v>6556713</v>
+        <v>6556848</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2345,7 +2344,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+          <t>Strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,6 +2353,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -2501,7 +2501,7 @@
         <v>122442770</v>
       </c>
       <c r="B18" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -1133,12 +1133,7 @@
         <v>122393382</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2036,12 +2031,7 @@
         <v>122418985</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56991492</v>
+        <v>122394081</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224363</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Etapp 13, Sörmlandsleden, Jämtarens NV-spets, 200m NNV om, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>632895.040306314</v>
+        <v>632906</v>
       </c>
       <c r="R2" t="n">
-        <v>6556913.741233928</v>
+        <v>6556844</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-02-14</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-02-14</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Måttligt stort bestånd</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,63 +766,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Något fuktig barrblandskog.</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Något fuktig barrblandskog.</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122263529</v>
+        <v>122418666</v>
       </c>
       <c r="B3" t="n">
-        <v>92115</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,22 +820,22 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>632862</v>
+        <v>632902</v>
       </c>
       <c r="R3" t="n">
-        <v>6556741</v>
+        <v>6556902</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Södermanland</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>Gnesta</t>
+          <t>Södertälje</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,17 +845,22 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Frustuna</t>
+          <t>Vårdinge</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-01-20</t>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov granlåga i en samling av gamla granlågor strax norr om bäcken.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,6 +869,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,60 +881,58 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122394626</v>
+        <v>122263529</v>
       </c>
       <c r="B4" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>632874</v>
+        <v>632862</v>
       </c>
       <c r="R4" t="n">
-        <v>6556728</v>
+        <v>6556741</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2025-01-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,49 +976,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist, Johan Björkstén, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122394081</v>
+        <v>122394464</v>
       </c>
       <c r="B5" t="n">
-        <v>91385</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,10 +1023,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>632906</v>
+        <v>632866</v>
       </c>
       <c r="R5" t="n">
-        <v>6556844</v>
+        <v>6556763</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,7 +1058,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1068,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,57 +1088,52 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122393382</v>
+        <v>122394575</v>
       </c>
       <c r="B6" t="n">
-        <v>57073</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>632867</v>
+        <v>632866</v>
       </c>
       <c r="R6" t="n">
-        <v>6557060</v>
+        <v>6556734</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1165,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1175,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,60 +1195,62 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122394575</v>
+        <v>122397142</v>
       </c>
       <c r="B7" t="n">
-        <v>92221</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björnmossen, Björnmossen, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>632866</v>
+        <v>632877</v>
       </c>
       <c r="R7" t="n">
-        <v>6556734</v>
+        <v>6556758</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1317,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,65 +1304,63 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Göran Ekström, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122393674</v>
+        <v>122418822</v>
       </c>
       <c r="B8" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>632870</v>
+        <v>632888</v>
       </c>
       <c r="R8" t="n">
-        <v>6556916</v>
+        <v>6556772</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,19 +1387,14 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:55</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal tall nära Sörmlandsleden.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,33 +1403,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122393735</v>
+        <v>122393382</v>
       </c>
       <c r="B9" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,34 +1433,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>632869</v>
+        <v>632867</v>
       </c>
       <c r="R9" t="n">
-        <v>6556877</v>
+        <v>6557060</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1497,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1507,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,67 +1527,63 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122397142</v>
+        <v>122418985</v>
       </c>
       <c r="B10" t="n">
-        <v>90960</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>632877</v>
+        <v>632876</v>
       </c>
       <c r="R10" t="n">
-        <v>6556758</v>
+        <v>6556713</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1658,19 +1610,14 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:32</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,27 +1632,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ekström</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ekström, Rolf Wahlström</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122394464</v>
+        <v>122419038</v>
       </c>
       <c r="B11" t="n">
-        <v>92221</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1713,37 +1655,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Djupsjön, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>632866</v>
+        <v>632878</v>
       </c>
       <c r="R11" t="n">
-        <v>6556763</v>
+        <v>6556686</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1770,19 +1720,14 @@
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:31</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:31</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färsk spillning.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,27 +1742,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122394484</v>
+        <v>122393674</v>
       </c>
       <c r="B12" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,10 +1789,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>632865</v>
+        <v>632870</v>
       </c>
       <c r="R12" t="n">
-        <v>6556760</v>
+        <v>6556916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1884,7 +1824,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1894,7 +1834,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1914,22 +1854,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122418572</v>
+        <v>122393735</v>
       </c>
       <c r="B13" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1937,41 +1872,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>632891</v>
+        <v>632869</v>
       </c>
       <c r="R13" t="n">
-        <v>6556848</v>
+        <v>6556877</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1998,40 +1929,49 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122418985</v>
+        <v>122394484</v>
       </c>
       <c r="B14" t="n">
-        <v>57073</v>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2039,45 +1979,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön, Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>632876</v>
+        <v>632865</v>
       </c>
       <c r="R14" t="n">
-        <v>6556713</v>
+        <v>6556760</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2104,14 +2036,19 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Färsk tjäderspillning. En tjäder kom flygande.</t>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,27 +2063,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Ulla Sebestyen, Rolf Wahlström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122421266</v>
+        <v>122394626</v>
       </c>
       <c r="B15" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2154,45 +2086,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön O om, Srm</t>
+          <t>Björnmossen, Björnmossen, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>632828</v>
+        <v>632874</v>
       </c>
       <c r="R15" t="n">
-        <v>6557060</v>
+        <v>6556728</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,14 +2143,19 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flertal ex.</t>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,44 +2164,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Gles barrskog.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122418563</v>
+        <v>122442770</v>
       </c>
       <c r="B16" t="n">
-        <v>97293</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,41 +2193,53 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>224361</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Äkta lopplummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Huperzia europaea</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Björk</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön, O om, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>632891</v>
+        <v>632838</v>
       </c>
       <c r="R16" t="n">
-        <v>6556848</v>
+        <v>6557241</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,7 +2273,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Strax norr om bäcken.</t>
+          <t>Enstaka vinterståndare.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,30 +2286,30 @@
       <c r="AG16" t="b">
         <v>0</v>
       </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Granskog.</t>
+        </is>
+      </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Rolf Wahlström, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122418533</v>
+        <v>122392583</v>
       </c>
       <c r="B17" t="n">
-        <v>100613</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,23 +2335,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupsjön, Ö om, Srm</t>
+          <t>Djupsjön, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>632875</v>
+        <v>632809</v>
       </c>
       <c r="R17" t="n">
-        <v>6557018</v>
+        <v>6557285</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2453,14 +2374,19 @@
           <t>2025-01-31</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>11:36</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Spridda ex inom fuktdråg.</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>11:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2469,34 +2395,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122442770</v>
+        <v>122418533</v>
       </c>
       <c r="B18" t="n">
-        <v>105461</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2504,53 +2424,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djupsjön, O om, Srm</t>
+          <t>Djupsjön, Ö om, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>632838</v>
+        <v>632875</v>
       </c>
       <c r="R18" t="n">
-        <v>6557241</v>
+        <v>6557018</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2584,7 +2492,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka vinterståndare.</t>
+          <t>Spridda ex inom fuktdråg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2597,23 +2505,459 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>Granskog.</t>
-        </is>
-      </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122418572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>632891</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556848</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122421266</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djupsjön O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>632828</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6557060</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Flertal ex.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Gles barrskog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
           <t>Rolf Wahlström</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Rolf Wahlström, Ulla Sebestyen</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122418563</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>224361</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Äkta lopplummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Huperzia europaea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Björk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djupsjön, Ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>632891</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556848</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Strax norr om bäcken.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Bo Karlsson, Rolf Wahlström, Johan Björkstén, Rolf Olsson, Ulla Sebestyen, Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>56991492</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Etapp 13, Sörmlandsleden, Jämtarens NV-spets, 200m NNV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>632895</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556914</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gnesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Frustuna</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2016-02-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2016-02-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Måttligt stort bestånd</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>Något fuktig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Något fuktig barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Rolf Wahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6539-2024 artfynd.xlsx
+++ b/artfynd/A 6539-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394081</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418666</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122263529</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394464</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394575</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122397142</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418822</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1531,6 +1571,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393382</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122419038</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393674</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1965,6 +2025,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122393735</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2072,6 +2137,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394484</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2179,6 +2249,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122394626</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2303,6 +2378,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122442770</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2410,6 +2490,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122392583</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2517,6 +2602,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418533</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2619,6 +2709,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418572</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2740,6 +2835,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122421266</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2847,6 +2947,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122418563</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,8 +3063,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56991492</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>